--- a/artfynd/A 17615-2025 artfynd.xlsx
+++ b/artfynd/A 17615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87217690</v>
+        <v>87217647</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,24 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lagerfors , Vg</t>
+          <t>Lagerfors, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449539.8348605544</v>
+        <v>449477</v>
       </c>
       <c r="R2" t="n">
-        <v>6491261.797184582</v>
+        <v>6491538</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +750,9 @@
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +764,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87217647</v>
+        <v>87217690</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,24 +818,20 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lagerfors, Vg</t>
+          <t>Lagerfors , Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449477.0123101304</v>
+        <v>449540</v>
       </c>
       <c r="R3" t="n">
-        <v>6491537.58354817</v>
+        <v>6491262</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,19 +861,9 @@
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,16 +875,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,12 +894,7 @@
         <v>95237919</v>
       </c>
       <c r="B4" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449543.560860771</v>
+        <v>449544</v>
       </c>
       <c r="R4" t="n">
-        <v>6491266.966975804</v>
+        <v>6491267</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,19 +962,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,12 +995,7 @@
         <v>102641693</v>
       </c>
       <c r="B5" t="n">
-        <v>39584</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449322.0288593754</v>
+        <v>449322</v>
       </c>
       <c r="R5" t="n">
-        <v>6491759.243759502</v>
+        <v>6491759</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1135,19 +1085,9 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,12 +1118,7 @@
         <v>102641874</v>
       </c>
       <c r="B6" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449488.9547333369</v>
+        <v>449489</v>
       </c>
       <c r="R6" t="n">
-        <v>6491329.243375122</v>
+        <v>6491329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,19 +1187,9 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,6 +1214,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102641884</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knulten, Lagerfors, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>449520</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6491230</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bällefors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Carina Lerdahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
